--- a/target/test-classes/LoginCredentialsTestData.xlsx
+++ b/target/test-classes/LoginCredentialsTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahadeva_R\Desktop\mahadev\opencart\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7673102C-FFFA-4C35-89AD-1EA23DFBE075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655E04A5-7902-443B-A5B3-5BCAB409D8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
